--- a/Documentation/Development/UseCaseTable.xlsx
+++ b/Documentation/Development/UseCaseTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30461751\Desktop\EarthShard\Documentation\Development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879E2010-9171-4E98-88FB-143F2611C011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E722826-3069-4ED7-AAF1-1A2CA883DCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40395" yWindow="4440" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
   <si>
     <t>Description of Test</t>
   </si>
@@ -48,9 +48,6 @@
     <t>player moved forward</t>
   </si>
   <si>
-    <t>non required</t>
-  </si>
-  <si>
     <t>pressing 's' should move player backward</t>
   </si>
   <si>
@@ -106,6 +103,105 @@
   </si>
   <si>
     <t>player jumping key and gravity</t>
+  </si>
+  <si>
+    <t>summon a rock projectile</t>
+  </si>
+  <si>
+    <t>right click should summon a rock and it should stay in place infront of the player</t>
+  </si>
+  <si>
+    <t>worked as expected</t>
+  </si>
+  <si>
+    <t>fire a summoned rock</t>
+  </si>
+  <si>
+    <t>a rock summoned by the player should shoot forward with left click and be affected by gravity</t>
+  </si>
+  <si>
+    <t>does as intended</t>
+  </si>
+  <si>
+    <t>check if rock destroys self on collision with sounds and particles</t>
+  </si>
+  <si>
+    <t>when a rock collides with an object it should destroy itself and play a particle effect and sound</t>
+  </si>
+  <si>
+    <t>works as intended</t>
+  </si>
+  <si>
+    <t>use ground raise ability to summon and destroy pillars</t>
+  </si>
+  <si>
+    <t>when right clicking with ground raise ability a pillar should be summoned or destroyed</t>
+  </si>
+  <si>
+    <t>works as expected</t>
+  </si>
+  <si>
+    <t>use the lift ability of the ground raise to raise the pillar to 5 meteres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when left clicking the pillar should raise up from the ground slowing at a cap of 5 meteres </t>
+  </si>
+  <si>
+    <t>switch ability with ability switch button</t>
+  </si>
+  <si>
+    <t>pressing 'q' should cycle between rock throw and ground raise and change crosshair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open form link on alpha pop up </t>
+  </si>
+  <si>
+    <t>pressing the link to form button should open up a URL to a form to fill out</t>
+  </si>
+  <si>
+    <t>close the alpha pop up</t>
+  </si>
+  <si>
+    <t>pressing close button on alpha pop up should close the panel</t>
+  </si>
+  <si>
+    <t>press play and open level select</t>
+  </si>
+  <si>
+    <t>pressing play button should open the level select screen and move camera to new area</t>
+  </si>
+  <si>
+    <t>return to menu from level select</t>
+  </si>
+  <si>
+    <t>pressing main menu button should move camera and open the main menu.</t>
+  </si>
+  <si>
+    <t>load level the dunes from level select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pressing the button titles the dunes should open the first level of the game </t>
+  </si>
+  <si>
+    <t xml:space="preserve">load level labyrinth </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pressing the button titled labyrinth should open the second level of the game </t>
+  </si>
+  <si>
+    <t>open the credits menu from main menu</t>
+  </si>
+  <si>
+    <t>pressing the credits button on the main menu should move camera and open the credits menu</t>
+  </si>
+  <si>
+    <t>quiting application from main menu</t>
+  </si>
+  <si>
+    <t>pressing quit to desktop option on main menu should quit to desktop</t>
+  </si>
+  <si>
+    <t>none required</t>
   </si>
 </sst>
 </file>
@@ -531,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>5</v>
@@ -540,7 +636,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -548,16 +644,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>9</v>
-      </c>
       <c r="E3" s="6" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -565,16 +661,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>11</v>
-      </c>
       <c r="E4" s="6" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -582,16 +678,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" s="6" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -599,16 +695,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="6" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -616,16 +712,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -633,143 +729,255 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="B13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="B14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="B15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+      <c r="B17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
+      <c r="B18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
+      <c r="B19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+      <c r="B21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+      <c r="B22" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
@@ -777,7 +985,9 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
+      <c r="D23" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -786,7 +996,9 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
+      <c r="D24" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -795,7 +1007,9 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
+      <c r="D25" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">

--- a/Documentation/Development/UseCaseTable.xlsx
+++ b/Documentation/Development/UseCaseTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30461751\Desktop\EarthShard\Documentation\Development\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Earth Shard\EarthShard\Documentation\Development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E722826-3069-4ED7-AAF1-1A2CA883DCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F06838-3892-4B89-BF32-469424A6A183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40395" yWindow="4440" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
   <si>
     <t>Description of Test</t>
   </si>
@@ -202,6 +202,69 @@
   </si>
   <si>
     <t>none required</t>
+  </si>
+  <si>
+    <t>return to menu from credits</t>
+  </si>
+  <si>
+    <t>take damage from enemy</t>
+  </si>
+  <si>
+    <t>enemy when throwing rock at player should cause the player to take 10 hp of damage</t>
+  </si>
+  <si>
+    <t>test enemy state switching</t>
+  </si>
+  <si>
+    <t>if enemy sees player they should move from patrol state too attack state</t>
+  </si>
+  <si>
+    <t>trigger level 1 doors</t>
+  </si>
+  <si>
+    <t>killing all enemies in an area should open a door</t>
+  </si>
+  <si>
+    <t>use switches to open a door</t>
+  </si>
+  <si>
+    <t>firing a rock at switches should activate them and when all 3 are active a door should open</t>
+  </si>
+  <si>
+    <t>level transition trigger</t>
+  </si>
+  <si>
+    <t>when touching the level transition trigger you should load into next scene</t>
+  </si>
+  <si>
+    <t>pausing the game</t>
+  </si>
+  <si>
+    <t>when player presses the pause button the game should freeze and a pause menu should pop up</t>
+  </si>
+  <si>
+    <t>pause return button</t>
+  </si>
+  <si>
+    <t>pressing return option in pause menu should return player to game, or if player presses escape again</t>
+  </si>
+  <si>
+    <t>pause restart level button</t>
+  </si>
+  <si>
+    <t>pressing this button should reload the current level</t>
+  </si>
+  <si>
+    <t>pause return to menu button</t>
+  </si>
+  <si>
+    <t>this button should return the player to the main menu</t>
+  </si>
+  <si>
+    <t>pause quit button</t>
+  </si>
+  <si>
+    <t>this button should quit the application.</t>
   </si>
 </sst>
 </file>
@@ -251,7 +314,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,6 +324,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -292,18 +361,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -312,7 +375,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -623,629 +698,695 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="D19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="D21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="6"/>
+      <c r="B23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="24" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="6"/>
+      <c r="B24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="25" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="6"/>
+      <c r="B25" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="26" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
+      <c r="B26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="27" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
+      <c r="B27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="28" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
+      <c r="B28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="29" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
+      <c r="B29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
+      <c r="B30" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="31" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
+      <c r="B31" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
+      <c r="B32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="33" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
+      <c r="B33" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="34" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
-        <v>33</v>
-      </c>
+      <c r="A34" s="5"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
     </row>
     <row r="35" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
-        <v>34</v>
-      </c>
+      <c r="A35" s="5"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
-        <v>35</v>
-      </c>
+      <c r="A36" s="5"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
     </row>
     <row r="37" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
-        <v>36</v>
-      </c>
+      <c r="A37" s="5"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
     </row>
     <row r="38" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
-        <v>37</v>
-      </c>
+      <c r="A38" s="5"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
     </row>
     <row r="39" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
-        <v>38</v>
-      </c>
+      <c r="A39" s="5"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
     </row>
     <row r="40" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
-        <v>39</v>
-      </c>
+      <c r="A40" s="5"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
     </row>
     <row r="41" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
-        <v>40</v>
-      </c>
+      <c r="A41" s="5"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
+      <c r="A42" s="7"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
+      <c r="A43" s="7"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
+      <c r="A44" s="7"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
+      <c r="A45" s="7"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
+      <c r="A46" s="7"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
+      <c r="A47" s="7"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
+      <c r="A48" s="7"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
+      <c r="A49" s="7"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
+      <c r="A50" s="7"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
+      <c r="A51" s="7"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
+      <c r="A52" s="7"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
+      <c r="A53" s="7"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
